--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0143.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0143.xlsx
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Khi ta đến đó, bọn Waveworn đã...</t>
+          <t>Khi tao đến đó, bọn Waveworn đã...</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>À, còn gì nữa... Bút! Đưa ta cái bút đây!</t>
+          <t>À, còn gì nữa... Bút! Đưa tao cái bút đây!</t>
         </is>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Nói thật thì họ giao chỗ này cho ta, nhưng ta thực sự không biết xử lý cái Thiết bị đầu cuối đó thế nào.</t>
+          <t>Nói thật thì họ giao chỗ này cho tao, nhưng tao thực sự không biết xử lý cái Thiết bị đầu cuối đó thế nào.</t>
         </is>
       </c>
     </row>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Ta đang xử lý đây! Chỉ còn vài con quái nguy hiểm nữa thôi, nhưng ta sẽ giải quyết xong.</t>
+          <t>Tao đang xử lý đây! Chỉ còn vài con quái nguy hiểm nữa thôi, nhưng tao sẽ giải quyết xong.</t>
         </is>
       </c>
     </row>
